--- a/support/aggregations/raw_to_aggregated.xlsx
+++ b/support/aggregations/raw_to_aggregated.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Activity"/>
@@ -2354,13 +2354,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2378,7 +2384,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -2407,10 +2420,10 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -5080,427 +5093,427 @@
     <col min="2" max="2" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B3" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="B4" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="2" t="s">
         <v>59</v>
       </c>
       <c r="B6" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
       <c r="B7" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B8" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B10" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B11" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="2" t="s">
         <v>66</v>
       </c>
       <c r="B13" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B14" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
       <c r="B15" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B16" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B17" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18" hidden="1">
       <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
       <c r="B19" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18" hidden="1">
       <c r="A20" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B20" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18" hidden="1">
       <c r="A21" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B21" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18" hidden="1">
       <c r="A22" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B22" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18" hidden="1">
       <c r="A23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B23" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18" hidden="1">
       <c r="A24" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B24" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18" hidden="1">
       <c r="A25" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B26" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B27" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B28" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18" hidden="1">
       <c r="A29" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B31" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B32" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B33" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18" hidden="1">
       <c r="A34" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B34" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="2" t="s">
         <v>89</v>
       </c>
       <c r="B36" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B37" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18" hidden="1">
       <c r="A38" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B38" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18" hidden="1">
       <c r="A39" s="2" t="s">
         <v>92</v>
       </c>
       <c r="B39" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18" hidden="1">
       <c r="A40" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B40" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B41" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B42" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B43" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B44" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B45" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B46" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B47" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="2" t="s">
         <v>101</v>
       </c>
       <c r="B48" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B49" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18" hidden="1">
       <c r="A50" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B50" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18" hidden="1">
       <c r="A51" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B51" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B52" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18" hidden="1">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B53" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="2" t="s">
         <v>107</v>
       </c>
       <c r="B54" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B55" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B56" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="2" t="s">
         <v>110</v>
       </c>
       <c r="B57" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B58" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B59" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="2" t="s">
         <v>113</v>
       </c>
       <c r="B60" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B61" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B62" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="2" t="s">
         <v>116</v>
       </c>
       <c r="B63" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="2" t="s">
         <v>117</v>
       </c>
       <c r="B64" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B65" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18" hidden="1">
       <c r="A66" s="2" t="s">
         <v>119</v>
       </c>
       <c r="B66" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18" hidden="1">
       <c r="A67" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B67" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B68" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="2" t="s">
         <v>122</v>
       </c>
       <c r="B69" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B70" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="2" t="s">
         <v>124</v>
       </c>
@@ -5530,7 +5543,7 @@
       </c>
       <c r="B75" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18" hidden="1">
       <c r="A76" s="2" t="s">
         <v>129</v>
       </c>
@@ -5548,7 +5561,7 @@
       </c>
       <c r="B78" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18" hidden="1">
       <c r="A79" s="2" t="s">
         <v>132</v>
       </c>
@@ -5560,7 +5573,7 @@
       </c>
       <c r="B80" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18" hidden="1">
       <c r="A81" s="2" t="s">
         <v>134</v>
       </c>
@@ -5590,7 +5603,7 @@
       </c>
       <c r="B85" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18" hidden="1">
       <c r="A86" s="2" t="s">
         <v>139</v>
       </c>
@@ -5608,7 +5621,7 @@
       </c>
       <c r="B88" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18" hidden="1">
       <c r="A89" s="2" t="s">
         <v>142</v>
       </c>
@@ -5638,13 +5651,13 @@
       </c>
       <c r="B93" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18" hidden="1">
       <c r="A94" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B94" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18" hidden="1">
       <c r="A95" s="2" t="s">
         <v>148</v>
       </c>
@@ -5692,13 +5705,13 @@
       </c>
       <c r="B102" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18" hidden="1">
       <c r="A103" s="2" t="s">
         <v>156</v>
       </c>
       <c r="B103" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18" hidden="1">
       <c r="A104" s="2" t="s">
         <v>157</v>
       </c>
@@ -5770,13 +5783,13 @@
       </c>
       <c r="B115" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18" hidden="1">
       <c r="A116" s="2" t="s">
         <v>169</v>
       </c>
       <c r="B116" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18" hidden="1">
       <c r="A117" s="2" t="s">
         <v>170</v>
       </c>
@@ -5788,7 +5801,7 @@
       </c>
       <c r="B118" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18" hidden="1">
       <c r="A119" s="2" t="s">
         <v>172</v>
       </c>
@@ -5866,13 +5879,13 @@
       </c>
       <c r="B131" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18" hidden="1">
       <c r="A132" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B132" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18" hidden="1">
       <c r="A133" s="2" t="s">
         <v>186</v>
       </c>
@@ -5926,7 +5939,7 @@
       </c>
       <c r="B141" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18" hidden="1">
       <c r="A142" s="2" t="s">
         <v>195</v>
       </c>
@@ -5944,7 +5957,7 @@
       </c>
       <c r="B144" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18" hidden="1">
       <c r="A145" s="2" t="s">
         <v>198</v>
       </c>
@@ -5956,7 +5969,7 @@
       </c>
       <c r="B146" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18" hidden="1">
       <c r="A147" s="2" t="s">
         <v>200</v>
       </c>
@@ -5986,7 +5999,7 @@
       </c>
       <c r="B151" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18" hidden="1">
       <c r="A152" s="2" t="s">
         <v>205</v>
       </c>
@@ -6004,7 +6017,7 @@
       </c>
       <c r="B154" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18" hidden="1">
       <c r="A155" s="2" t="s">
         <v>208</v>
       </c>
@@ -6034,13 +6047,13 @@
       </c>
       <c r="B159" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18" hidden="1">
       <c r="A160" s="2" t="s">
         <v>213</v>
       </c>
       <c r="B160" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18" hidden="1">
       <c r="A161" s="2" t="s">
         <v>214</v>
       </c>
@@ -6088,7 +6101,7 @@
       </c>
       <c r="B168" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18" hidden="1">
       <c r="A169" s="2" t="s">
         <v>222</v>
       </c>
@@ -6154,13 +6167,13 @@
       </c>
       <c r="B179" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18" hidden="1">
       <c r="A180" s="2" t="s">
         <v>233</v>
       </c>
       <c r="B180" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18" hidden="1">
       <c r="A181" s="2" t="s">
         <v>234</v>
       </c>
@@ -6172,7 +6185,7 @@
       </c>
       <c r="B182" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18" hidden="1">
       <c r="A183" s="2" t="s">
         <v>236</v>
       </c>
@@ -6190,13 +6203,13 @@
       </c>
       <c r="B185" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18" hidden="1">
       <c r="A186" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B186" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18" hidden="1">
       <c r="A187" s="2" t="s">
         <v>240</v>
       </c>
@@ -6238,7 +6251,7 @@
       </c>
       <c r="B193" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18" hidden="1">
       <c r="A194" s="2" t="s">
         <v>247</v>
       </c>
@@ -6250,7 +6263,7 @@
       </c>
       <c r="B195" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18" hidden="1">
       <c r="A196" s="2" t="s">
         <v>249</v>
       </c>
@@ -6268,13 +6281,13 @@
       </c>
       <c r="B198" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18" hidden="1">
       <c r="A199" s="2" t="s">
         <v>252</v>
       </c>
       <c r="B199" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18" hidden="1">
       <c r="A200" s="2" t="s">
         <v>253</v>
       </c>
@@ -6286,7 +6299,7 @@
       </c>
       <c r="B201" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18" hidden="1">
       <c r="A202" s="2" t="s">
         <v>255</v>
       </c>
@@ -6304,13 +6317,13 @@
       </c>
       <c r="B204" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18" hidden="1">
       <c r="A205" s="2" t="s">
         <v>258</v>
       </c>
       <c r="B205" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18" hidden="1">
       <c r="A206" s="2" t="s">
         <v>259</v>
       </c>
@@ -6352,7 +6365,7 @@
       </c>
       <c r="B212" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18" hidden="1">
       <c r="A213" s="2" t="s">
         <v>266</v>
       </c>
@@ -6364,7 +6377,7 @@
       </c>
       <c r="B214" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18" hidden="1">
       <c r="A215" s="2" t="s">
         <v>268</v>
       </c>
@@ -6382,13 +6395,13 @@
       </c>
       <c r="B217" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18" hidden="1">
       <c r="A218" s="2" t="s">
         <v>271</v>
       </c>
       <c r="B218" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18" hidden="1">
       <c r="A219" s="2" t="s">
         <v>272</v>
       </c>
@@ -6400,7 +6413,7 @@
       </c>
       <c r="B220" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18" hidden="1">
       <c r="A221" s="2" t="s">
         <v>274</v>
       </c>
@@ -6418,13 +6431,13 @@
       </c>
       <c r="B223" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18" hidden="1">
       <c r="A224" s="2" t="s">
         <v>277</v>
       </c>
       <c r="B224" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18" hidden="1">
       <c r="A225" s="2" t="s">
         <v>278</v>
       </c>
@@ -6466,7 +6479,7 @@
       </c>
       <c r="B231" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18" hidden="1">
       <c r="A232" s="2" t="s">
         <v>285</v>
       </c>
@@ -6478,7 +6491,7 @@
       </c>
       <c r="B233" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18" hidden="1">
       <c r="A234" s="2" t="s">
         <v>287</v>
       </c>
@@ -6496,13 +6509,13 @@
       </c>
       <c r="B236" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18" hidden="1">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
       <c r="B237" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18" hidden="1">
       <c r="A238" s="2" t="s">
         <v>291</v>
       </c>
@@ -6514,7 +6527,7 @@
       </c>
       <c r="B239" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18" hidden="1">
       <c r="A240" s="2" t="s">
         <v>293</v>
       </c>
@@ -6532,13 +6545,13 @@
       </c>
       <c r="B242" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18" hidden="1">
       <c r="A243" s="2" t="s">
         <v>296</v>
       </c>
       <c r="B243" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18" hidden="1">
       <c r="A244" s="2" t="s">
         <v>297</v>
       </c>
@@ -6580,7 +6593,7 @@
       </c>
       <c r="B250" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18" hidden="1">
       <c r="A251" s="2" t="s">
         <v>304</v>
       </c>
@@ -6592,7 +6605,7 @@
       </c>
       <c r="B252" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18" hidden="1">
       <c r="A253" s="2" t="s">
         <v>306</v>
       </c>
@@ -6610,13 +6623,13 @@
       </c>
       <c r="B255" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18" hidden="1">
       <c r="A256" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B256" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="18" hidden="1">
       <c r="A257" s="2" t="s">
         <v>310</v>
       </c>
@@ -6628,7 +6641,7 @@
       </c>
       <c r="B258" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18" hidden="1">
       <c r="A259" s="2" t="s">
         <v>312</v>
       </c>
@@ -6646,13 +6659,13 @@
       </c>
       <c r="B261" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18" hidden="1">
       <c r="A262" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B262" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18" hidden="1">
       <c r="A263" s="2" t="s">
         <v>316</v>
       </c>
@@ -6694,7 +6707,7 @@
       </c>
       <c r="B269" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18" hidden="1">
       <c r="A270" s="2" t="s">
         <v>323</v>
       </c>
@@ -6706,7 +6719,7 @@
       </c>
       <c r="B271" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18" hidden="1">
       <c r="A272" s="2" t="s">
         <v>325</v>
       </c>
@@ -6724,13 +6737,13 @@
       </c>
       <c r="B274" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18" hidden="1">
       <c r="A275" s="2" t="s">
         <v>328</v>
       </c>
       <c r="B275" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18" hidden="1">
       <c r="A276" s="2" t="s">
         <v>329</v>
       </c>
@@ -6742,7 +6755,7 @@
       </c>
       <c r="B277" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18" hidden="1">
       <c r="A278" s="2" t="s">
         <v>331</v>
       </c>
@@ -6760,13 +6773,13 @@
       </c>
       <c r="B280" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18" hidden="1">
       <c r="A281" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B281" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18" hidden="1">
       <c r="A282" s="2" t="s">
         <v>335</v>
       </c>
@@ -6808,7 +6821,7 @@
       </c>
       <c r="B288" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="18" hidden="1">
       <c r="A289" s="2" t="s">
         <v>342</v>
       </c>
@@ -6820,7 +6833,7 @@
       </c>
       <c r="B290" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="18" hidden="1">
       <c r="A291" s="2" t="s">
         <v>344</v>
       </c>
@@ -6838,13 +6851,13 @@
       </c>
       <c r="B293" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="18" hidden="1">
       <c r="A294" s="2" t="s">
         <v>347</v>
       </c>
       <c r="B294" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="18" hidden="1">
       <c r="A295" s="2" t="s">
         <v>348</v>
       </c>
@@ -6856,7 +6869,7 @@
       </c>
       <c r="B296" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="18" hidden="1">
       <c r="A297" s="2" t="s">
         <v>350</v>
       </c>
@@ -6874,13 +6887,13 @@
       </c>
       <c r="B299" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="18" hidden="1">
       <c r="A300" s="2" t="s">
         <v>353</v>
       </c>
       <c r="B300" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="18" hidden="1">
       <c r="A301" s="2" t="s">
         <v>354</v>
       </c>
@@ -6922,7 +6935,7 @@
       </c>
       <c r="B307" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="18" hidden="1">
       <c r="A308" s="2" t="s">
         <v>361</v>
       </c>
@@ -6934,37 +6947,37 @@
       </c>
       <c r="B309" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="18" hidden="1">
       <c r="A310" s="2" t="s">
         <v>363</v>
       </c>
       <c r="B310" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="18" hidden="1">
       <c r="A311" s="2" t="s">
         <v>364</v>
       </c>
       <c r="B311" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="18" hidden="1">
       <c r="A312" s="2" t="s">
         <v>365</v>
       </c>
       <c r="B312" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="18" hidden="1">
       <c r="A313" s="2" t="s">
         <v>366</v>
       </c>
       <c r="B313" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="18" hidden="1">
       <c r="A314" s="2" t="s">
         <v>367</v>
       </c>
       <c r="B314" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="18" hidden="1">
       <c r="A315" s="2" t="s">
         <v>368</v>
       </c>
@@ -6982,7 +6995,7 @@
       </c>
       <c r="B317" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="18" hidden="1">
       <c r="A318" s="2" t="s">
         <v>371</v>
       </c>
@@ -7000,13 +7013,13 @@
       </c>
       <c r="B320" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="18" hidden="1">
       <c r="A321" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B321" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="18" hidden="1">
       <c r="A322" s="2" t="s">
         <v>375</v>
       </c>
@@ -7018,7 +7031,7 @@
       </c>
       <c r="B323" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="18" hidden="1">
       <c r="A324" s="2" t="s">
         <v>377</v>
       </c>
@@ -7036,13 +7049,13 @@
       </c>
       <c r="B326" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="18" hidden="1">
       <c r="A327" s="2" t="s">
         <v>380</v>
       </c>
       <c r="B327" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="18" hidden="1">
       <c r="A328" s="2" t="s">
         <v>381</v>
       </c>
@@ -7084,7 +7097,7 @@
       </c>
       <c r="B334" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="18" hidden="1">
       <c r="A335" s="2" t="s">
         <v>388</v>
       </c>
@@ -7096,7 +7109,7 @@
       </c>
       <c r="B336" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="18" hidden="1">
       <c r="A337" s="2" t="s">
         <v>390</v>
       </c>
